--- a/output/pdf_financials_xlsx/KOG.xlsx
+++ b/output/pdf_financials_xlsx/KOG.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>6.1e-05</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.532338</v>
+        <v>-0.532447</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.450261</v>
+        <v>-2.450313</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.370709</v>
+        <v>-1.37077</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.532338</v>
+        <v>-0.532447</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.450261</v>
+        <v>-2.450313</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.370709</v>
+        <v>-1.37077</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.51124</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.779576</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.235401</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.51124</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.779576</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.235401</v>
       </c>
     </row>
     <row r="37">
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.527608</v>
+        <v>0.016368</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.817568</v>
+        <v>0.037992</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">

--- a/output/pdf_financials_xlsx/KOG.xlsx
+++ b/output/pdf_financials_xlsx/KOG.xlsx
@@ -1518,13 +1518,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.035422</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.064347</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="68">
